--- a/data/napoli/service_status.xlsx
+++ b/data/napoli/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,332 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Traction_Converter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fren Rezistörü</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:58</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:46</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-06 01:14:47</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/napoli/service_status.xlsx
+++ b/data/napoli/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,6 @@
           <t>Fren Rezistörü</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-04-06 01:14:58</t>
@@ -779,6 +778,383 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:43</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:59</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:03</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:04</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:57:50</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:59:36</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/napoli/service_status.xlsx
+++ b/data/napoli/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,15 +1146,334 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-04-09 00:59:36</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:10</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:10</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:11</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-04-12 16:00:12</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
